--- a/artfynd/A 56053-2024 artfynd.xlsx
+++ b/artfynd/A 56053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150072</v>
+        <v>121152203</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>91380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675101</v>
+        <v>675160</v>
       </c>
       <c r="R2" t="n">
-        <v>7143875</v>
+        <v>7143980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152454</v>
+        <v>121152204</v>
       </c>
       <c r="B3" t="n">
-        <v>79216</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675148</v>
+        <v>675118</v>
       </c>
       <c r="R3" t="n">
-        <v>7143990</v>
+        <v>7143900</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150071</v>
+        <v>121152454</v>
       </c>
       <c r="B4" t="n">
-        <v>90652</v>
+        <v>79219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675240</v>
+        <v>675148</v>
       </c>
       <c r="R4" t="n">
-        <v>7144063</v>
+        <v>7143990</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152207</v>
+        <v>121150072</v>
       </c>
       <c r="B5" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675254</v>
+        <v>675101</v>
       </c>
       <c r="R5" t="n">
-        <v>7144060</v>
+        <v>7143875</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152204</v>
+        <v>121150071</v>
       </c>
       <c r="B6" t="n">
-        <v>90973</v>
+        <v>90662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675118</v>
+        <v>675240</v>
       </c>
       <c r="R6" t="n">
-        <v>7143900</v>
+        <v>7144063</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152455</v>
+        <v>121152207</v>
       </c>
       <c r="B7" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675102</v>
+        <v>675254</v>
       </c>
       <c r="R7" t="n">
-        <v>7143880</v>
+        <v>7144060</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152203</v>
+        <v>121152455</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>90715</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675160</v>
+        <v>675102</v>
       </c>
       <c r="R8" t="n">
-        <v>7143980</v>
+        <v>7143880</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 56053-2024 artfynd.xlsx
+++ b/artfynd/A 56053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152203</v>
+        <v>121152204</v>
       </c>
       <c r="B2" t="n">
-        <v>91380</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675160</v>
+        <v>675118</v>
       </c>
       <c r="R2" t="n">
-        <v>7143980</v>
+        <v>7143900</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152204</v>
+        <v>121152207</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675118</v>
+        <v>675254</v>
       </c>
       <c r="R3" t="n">
-        <v>7143900</v>
+        <v>7144060</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152454</v>
+        <v>121150072</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>90715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675148</v>
+        <v>675101</v>
       </c>
       <c r="R4" t="n">
-        <v>7143990</v>
+        <v>7143875</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150072</v>
+        <v>121150071</v>
       </c>
       <c r="B5" t="n">
-        <v>90715</v>
+        <v>90662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675101</v>
+        <v>675240</v>
       </c>
       <c r="R5" t="n">
-        <v>7143875</v>
+        <v>7144063</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150071</v>
+        <v>121152455</v>
       </c>
       <c r="B6" t="n">
-        <v>90662</v>
+        <v>90715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675240</v>
+        <v>675102</v>
       </c>
       <c r="R6" t="n">
-        <v>7144063</v>
+        <v>7143880</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152207</v>
+        <v>121152203</v>
       </c>
       <c r="B7" t="n">
-        <v>90715</v>
+        <v>91380</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675254</v>
+        <v>675160</v>
       </c>
       <c r="R7" t="n">
-        <v>7144060</v>
+        <v>7143980</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152455</v>
+        <v>121152454</v>
       </c>
       <c r="B8" t="n">
-        <v>90715</v>
+        <v>79219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675102</v>
+        <v>675148</v>
       </c>
       <c r="R8" t="n">
-        <v>7143880</v>
+        <v>7143990</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 56053-2024 artfynd.xlsx
+++ b/artfynd/A 56053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152204</v>
+        <v>121152203</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>91392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675118</v>
+        <v>675160</v>
       </c>
       <c r="R2" t="n">
-        <v>7143900</v>
+        <v>7143980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152207</v>
+        <v>121152204</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>90995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675254</v>
+        <v>675118</v>
       </c>
       <c r="R3" t="n">
-        <v>7144060</v>
+        <v>7143900</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121150072</v>
       </c>
       <c r="B4" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150071</v>
+        <v>121152454</v>
       </c>
       <c r="B5" t="n">
-        <v>90662</v>
+        <v>79222</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675240</v>
+        <v>675148</v>
       </c>
       <c r="R5" t="n">
-        <v>7144063</v>
+        <v>7143990</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152455</v>
+        <v>121152207</v>
       </c>
       <c r="B6" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675102</v>
+        <v>675254</v>
       </c>
       <c r="R6" t="n">
-        <v>7143880</v>
+        <v>7144060</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152203</v>
+        <v>121152455</v>
       </c>
       <c r="B7" t="n">
-        <v>91380</v>
+        <v>90727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675160</v>
+        <v>675102</v>
       </c>
       <c r="R7" t="n">
-        <v>7143980</v>
+        <v>7143880</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152454</v>
+        <v>121150071</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>90674</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675148</v>
+        <v>675240</v>
       </c>
       <c r="R8" t="n">
-        <v>7143990</v>
+        <v>7144063</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 56053-2024 artfynd.xlsx
+++ b/artfynd/A 56053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152203</v>
+        <v>121150071</v>
       </c>
       <c r="B2" t="n">
-        <v>91392</v>
+        <v>90675</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675160</v>
+        <v>675240</v>
       </c>
       <c r="R2" t="n">
-        <v>7143980</v>
+        <v>7144063</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152204</v>
+        <v>121152455</v>
       </c>
       <c r="B3" t="n">
-        <v>90995</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675118</v>
+        <v>675102</v>
       </c>
       <c r="R3" t="n">
-        <v>7143900</v>
+        <v>7143880</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>121150072</v>
       </c>
       <c r="B4" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152454</v>
+        <v>121152207</v>
       </c>
       <c r="B5" t="n">
-        <v>79222</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675148</v>
+        <v>675254</v>
       </c>
       <c r="R5" t="n">
-        <v>7143990</v>
+        <v>7144060</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152207</v>
+        <v>121152204</v>
       </c>
       <c r="B6" t="n">
-        <v>90727</v>
+        <v>90996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675254</v>
+        <v>675118</v>
       </c>
       <c r="R6" t="n">
-        <v>7144060</v>
+        <v>7143900</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152455</v>
+        <v>121152454</v>
       </c>
       <c r="B7" t="n">
-        <v>90727</v>
+        <v>79222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675102</v>
+        <v>675148</v>
       </c>
       <c r="R7" t="n">
-        <v>7143880</v>
+        <v>7143990</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121150071</v>
+        <v>121152203</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
+        <v>91393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675240</v>
+        <v>675160</v>
       </c>
       <c r="R8" t="n">
-        <v>7144063</v>
+        <v>7143980</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 56053-2024 artfynd.xlsx
+++ b/artfynd/A 56053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150071</v>
+        <v>121152203</v>
       </c>
       <c r="B2" t="n">
-        <v>90675</v>
+        <v>91396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675240</v>
+        <v>675160</v>
       </c>
       <c r="R2" t="n">
-        <v>7144063</v>
+        <v>7143980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152455</v>
+        <v>121152204</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>90999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675102</v>
+        <v>675118</v>
       </c>
       <c r="R3" t="n">
-        <v>7143880</v>
+        <v>7143900</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>121150072</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152207</v>
+        <v>121152454</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>79225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675254</v>
+        <v>675148</v>
       </c>
       <c r="R5" t="n">
-        <v>7144060</v>
+        <v>7143990</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152204</v>
+        <v>121150071</v>
       </c>
       <c r="B6" t="n">
-        <v>90996</v>
+        <v>90678</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675118</v>
+        <v>675240</v>
       </c>
       <c r="R6" t="n">
-        <v>7143900</v>
+        <v>7144063</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152454</v>
+        <v>121152207</v>
       </c>
       <c r="B7" t="n">
-        <v>79222</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675148</v>
+        <v>675254</v>
       </c>
       <c r="R7" t="n">
-        <v>7143990</v>
+        <v>7144060</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152203</v>
+        <v>121152455</v>
       </c>
       <c r="B8" t="n">
-        <v>91393</v>
+        <v>90731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675160</v>
+        <v>675102</v>
       </c>
       <c r="R8" t="n">
-        <v>7143980</v>
+        <v>7143880</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 56053-2024 artfynd.xlsx
+++ b/artfynd/A 56053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152203</v>
+        <v>121152207</v>
       </c>
       <c r="B2" t="n">
-        <v>91396</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675160</v>
+        <v>675254</v>
       </c>
       <c r="R2" t="n">
-        <v>7143980</v>
+        <v>7144060</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152204</v>
+        <v>121150072</v>
       </c>
       <c r="B3" t="n">
-        <v>90999</v>
+        <v>90731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675118</v>
+        <v>675101</v>
       </c>
       <c r="R3" t="n">
-        <v>7143900</v>
+        <v>7143875</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150072</v>
+        <v>121150071</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>90678</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675101</v>
+        <v>675240</v>
       </c>
       <c r="R4" t="n">
-        <v>7143875</v>
+        <v>7144063</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152454</v>
+        <v>121152204</v>
       </c>
       <c r="B5" t="n">
-        <v>79225</v>
+        <v>90999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675148</v>
+        <v>675118</v>
       </c>
       <c r="R5" t="n">
-        <v>7143990</v>
+        <v>7143900</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150071</v>
+        <v>121152455</v>
       </c>
       <c r="B6" t="n">
-        <v>90678</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675240</v>
+        <v>675102</v>
       </c>
       <c r="R6" t="n">
-        <v>7144063</v>
+        <v>7143880</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152207</v>
+        <v>121152454</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>79225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675254</v>
+        <v>675148</v>
       </c>
       <c r="R7" t="n">
-        <v>7144060</v>
+        <v>7143990</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152455</v>
+        <v>121152203</v>
       </c>
       <c r="B8" t="n">
-        <v>90731</v>
+        <v>91396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675102</v>
+        <v>675160</v>
       </c>
       <c r="R8" t="n">
-        <v>7143880</v>
+        <v>7143980</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
